--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4460,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124288644</v>
+        <v>124288656</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,21 +4476,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555774</v>
+        <v>555769</v>
       </c>
       <c r="R34" t="n">
-        <v>6696769</v>
+        <v>6696795</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124288646</v>
+        <v>124288644</v>
       </c>
       <c r="B35" t="n">
         <v>91012</v>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555732</v>
+        <v>555774</v>
       </c>
       <c r="R35" t="n">
-        <v>6696815</v>
+        <v>6696769</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288655</v>
+        <v>124288645</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555733</v>
+        <v>555769</v>
       </c>
       <c r="R36" t="n">
-        <v>6696827</v>
+        <v>6696795</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124288656</v>
+        <v>124288654</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4778,25 +4778,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555769</v>
+        <v>555776</v>
       </c>
       <c r="R37" t="n">
-        <v>6696795</v>
+        <v>6696789</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288654</v>
+        <v>124288646</v>
       </c>
       <c r="B38" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4880,25 +4880,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555776</v>
+        <v>555732</v>
       </c>
       <c r="R38" t="n">
-        <v>6696789</v>
+        <v>6696815</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124288645</v>
+        <v>124288655</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555769</v>
+        <v>555733</v>
       </c>
       <c r="R39" t="n">
-        <v>6696795</v>
+        <v>6696827</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4460,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124288656</v>
+        <v>124288646</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,21 +4476,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555769</v>
+        <v>555732</v>
       </c>
       <c r="R34" t="n">
-        <v>6696795</v>
+        <v>6696815</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288645</v>
+        <v>124288654</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4676,25 +4676,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555769</v>
+        <v>555776</v>
       </c>
       <c r="R36" t="n">
-        <v>6696795</v>
+        <v>6696789</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124288654</v>
+        <v>124288656</v>
       </c>
       <c r="B37" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4778,25 +4778,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555776</v>
+        <v>555769</v>
       </c>
       <c r="R37" t="n">
-        <v>6696789</v>
+        <v>6696795</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288646</v>
+        <v>124288655</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555732</v>
+        <v>555733</v>
       </c>
       <c r="R38" t="n">
-        <v>6696815</v>
+        <v>6696827</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124288655</v>
+        <v>124288645</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555733</v>
+        <v>555769</v>
       </c>
       <c r="R39" t="n">
-        <v>6696827</v>
+        <v>6696795</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4562,10 +4562,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124288644</v>
+        <v>124288655</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4578,21 +4578,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555774</v>
+        <v>555733</v>
       </c>
       <c r="R35" t="n">
-        <v>6696769</v>
+        <v>6696827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288654</v>
+        <v>124288656</v>
       </c>
       <c r="B36" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4676,25 +4676,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555776</v>
+        <v>555769</v>
       </c>
       <c r="R36" t="n">
-        <v>6696789</v>
+        <v>6696795</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124288656</v>
+        <v>124288654</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4778,25 +4778,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555769</v>
+        <v>555776</v>
       </c>
       <c r="R37" t="n">
-        <v>6696795</v>
+        <v>6696789</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288655</v>
+        <v>124288644</v>
       </c>
       <c r="B38" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555733</v>
+        <v>555774</v>
       </c>
       <c r="R38" t="n">
-        <v>6696827</v>
+        <v>6696769</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4460,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124288646</v>
+        <v>124288654</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4472,25 +4472,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555732</v>
+        <v>555776</v>
       </c>
       <c r="R34" t="n">
-        <v>6696815</v>
+        <v>6696789</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4562,10 +4562,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124288655</v>
+        <v>124288646</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4578,21 +4578,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555733</v>
+        <v>555732</v>
       </c>
       <c r="R35" t="n">
-        <v>6696827</v>
+        <v>6696815</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288656</v>
+        <v>124288644</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555769</v>
+        <v>555774</v>
       </c>
       <c r="R36" t="n">
-        <v>6696795</v>
+        <v>6696769</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124288654</v>
+        <v>124288656</v>
       </c>
       <c r="B37" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4778,25 +4778,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555776</v>
+        <v>555769</v>
       </c>
       <c r="R37" t="n">
-        <v>6696789</v>
+        <v>6696795</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288644</v>
+        <v>124288655</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555774</v>
+        <v>555733</v>
       </c>
       <c r="R38" t="n">
-        <v>6696769</v>
+        <v>6696827</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4460,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124288654</v>
+        <v>124288656</v>
       </c>
       <c r="B34" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4472,25 +4472,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555776</v>
+        <v>555769</v>
       </c>
       <c r="R34" t="n">
-        <v>6696789</v>
+        <v>6696795</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4562,10 +4562,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124288646</v>
+        <v>124288655</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4578,21 +4578,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555732</v>
+        <v>555733</v>
       </c>
       <c r="R35" t="n">
-        <v>6696815</v>
+        <v>6696827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288644</v>
+        <v>124288654</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4676,25 +4676,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555774</v>
+        <v>555776</v>
       </c>
       <c r="R36" t="n">
-        <v>6696769</v>
+        <v>6696789</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124288656</v>
+        <v>124288646</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555769</v>
+        <v>555732</v>
       </c>
       <c r="R37" t="n">
-        <v>6696795</v>
+        <v>6696815</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288655</v>
+        <v>124288644</v>
       </c>
       <c r="B38" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555733</v>
+        <v>555774</v>
       </c>
       <c r="R38" t="n">
-        <v>6696827</v>
+        <v>6696769</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4460,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124288656</v>
+        <v>124288644</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,21 +4476,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555769</v>
+        <v>555774</v>
       </c>
       <c r="R34" t="n">
-        <v>6696795</v>
+        <v>6696769</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4562,10 +4562,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124288655</v>
+        <v>124288654</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4574,25 +4574,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555733</v>
+        <v>555776</v>
       </c>
       <c r="R35" t="n">
-        <v>6696827</v>
+        <v>6696789</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288654</v>
+        <v>124288655</v>
       </c>
       <c r="B36" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4676,25 +4676,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555776</v>
+        <v>555733</v>
       </c>
       <c r="R36" t="n">
-        <v>6696789</v>
+        <v>6696827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124288646</v>
+        <v>124288645</v>
       </c>
       <c r="B37" t="n">
         <v>91012</v>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555732</v>
+        <v>555769</v>
       </c>
       <c r="R37" t="n">
-        <v>6696815</v>
+        <v>6696795</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288644</v>
+        <v>124288646</v>
       </c>
       <c r="B38" t="n">
         <v>91012</v>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555774</v>
+        <v>555732</v>
       </c>
       <c r="R38" t="n">
-        <v>6696769</v>
+        <v>6696815</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124288645</v>
+        <v>124288656</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4460,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124288644</v>
+        <v>124288654</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4472,25 +4472,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555774</v>
+        <v>555776</v>
       </c>
       <c r="R34" t="n">
-        <v>6696769</v>
+        <v>6696789</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4562,10 +4562,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124288654</v>
+        <v>124288644</v>
       </c>
       <c r="B35" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4574,25 +4574,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555776</v>
+        <v>555774</v>
       </c>
       <c r="R35" t="n">
-        <v>6696789</v>
+        <v>6696769</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288655</v>
+        <v>124288656</v>
       </c>
       <c r="B36" t="n">
         <v>91299</v>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555733</v>
+        <v>555769</v>
       </c>
       <c r="R36" t="n">
-        <v>6696827</v>
+        <v>6696795</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288646</v>
+        <v>124288655</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555732</v>
+        <v>555733</v>
       </c>
       <c r="R38" t="n">
-        <v>6696815</v>
+        <v>6696827</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124288656</v>
+        <v>124288646</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555769</v>
+        <v>555732</v>
       </c>
       <c r="R39" t="n">
-        <v>6696795</v>
+        <v>6696815</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4460,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124288654</v>
+        <v>124288656</v>
       </c>
       <c r="B34" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4472,25 +4472,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555776</v>
+        <v>555769</v>
       </c>
       <c r="R34" t="n">
-        <v>6696789</v>
+        <v>6696795</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124288644</v>
+        <v>124288646</v>
       </c>
       <c r="B35" t="n">
         <v>91012</v>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555774</v>
+        <v>555732</v>
       </c>
       <c r="R35" t="n">
-        <v>6696769</v>
+        <v>6696815</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288656</v>
+        <v>124288654</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4676,25 +4676,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555769</v>
+        <v>555776</v>
       </c>
       <c r="R36" t="n">
-        <v>6696795</v>
+        <v>6696789</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124288645</v>
+        <v>124288655</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555769</v>
+        <v>555733</v>
       </c>
       <c r="R37" t="n">
-        <v>6696795</v>
+        <v>6696827</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288655</v>
+        <v>124288644</v>
       </c>
       <c r="B38" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555733</v>
+        <v>555774</v>
       </c>
       <c r="R38" t="n">
-        <v>6696827</v>
+        <v>6696769</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4970,7 +4970,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124288646</v>
+        <v>124288645</v>
       </c>
       <c r="B39" t="n">
         <v>91012</v>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555732</v>
+        <v>555769</v>
       </c>
       <c r="R39" t="n">
-        <v>6696815</v>
+        <v>6696795</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4460,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124288656</v>
+        <v>124288645</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,21 +4476,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124288646</v>
+        <v>124288656</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4578,21 +4578,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555732</v>
+        <v>555769</v>
       </c>
       <c r="R35" t="n">
-        <v>6696815</v>
+        <v>6696795</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288654</v>
+        <v>124288655</v>
       </c>
       <c r="B36" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4676,25 +4676,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555776</v>
+        <v>555733</v>
       </c>
       <c r="R36" t="n">
-        <v>6696789</v>
+        <v>6696827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124288655</v>
+        <v>124288654</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4778,25 +4778,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555733</v>
+        <v>555776</v>
       </c>
       <c r="R37" t="n">
-        <v>6696827</v>
+        <v>6696789</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288644</v>
+        <v>124288646</v>
       </c>
       <c r="B38" t="n">
         <v>91012</v>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555774</v>
+        <v>555732</v>
       </c>
       <c r="R38" t="n">
-        <v>6696769</v>
+        <v>6696815</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4970,7 +4970,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124288645</v>
+        <v>124288644</v>
       </c>
       <c r="B39" t="n">
         <v>91012</v>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555769</v>
+        <v>555774</v>
       </c>
       <c r="R39" t="n">
-        <v>6696795</v>
+        <v>6696769</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4460,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124288645</v>
+        <v>124288655</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,21 +4476,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555769</v>
+        <v>555733</v>
       </c>
       <c r="R34" t="n">
-        <v>6696795</v>
+        <v>6696827</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4562,10 +4562,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124288656</v>
+        <v>124288654</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4574,25 +4574,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555769</v>
+        <v>555776</v>
       </c>
       <c r="R35" t="n">
-        <v>6696795</v>
+        <v>6696789</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288655</v>
+        <v>124288656</v>
       </c>
       <c r="B36" t="n">
         <v>91299</v>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555733</v>
+        <v>555769</v>
       </c>
       <c r="R36" t="n">
-        <v>6696827</v>
+        <v>6696795</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124288654</v>
+        <v>124288644</v>
       </c>
       <c r="B37" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4778,25 +4778,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555776</v>
+        <v>555774</v>
       </c>
       <c r="R37" t="n">
-        <v>6696789</v>
+        <v>6696769</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288646</v>
+        <v>124288645</v>
       </c>
       <c r="B38" t="n">
         <v>91012</v>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555732</v>
+        <v>555769</v>
       </c>
       <c r="R38" t="n">
-        <v>6696815</v>
+        <v>6696795</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4970,7 +4970,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124288644</v>
+        <v>124288646</v>
       </c>
       <c r="B39" t="n">
         <v>91012</v>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555774</v>
+        <v>555732</v>
       </c>
       <c r="R39" t="n">
-        <v>6696769</v>
+        <v>6696815</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4664,10 +4664,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288656</v>
+        <v>124288645</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288645</v>
+        <v>124288646</v>
       </c>
       <c r="B38" t="n">
         <v>91012</v>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555769</v>
+        <v>555732</v>
       </c>
       <c r="R38" t="n">
-        <v>6696795</v>
+        <v>6696815</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124288646</v>
+        <v>124288656</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4986,21 +4986,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555732</v>
+        <v>555769</v>
       </c>
       <c r="R39" t="n">
-        <v>6696815</v>
+        <v>6696795</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4460,7 +4460,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124288655</v>
+        <v>124288656</v>
       </c>
       <c r="B34" t="n">
         <v>91299</v>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555733</v>
+        <v>555769</v>
       </c>
       <c r="R34" t="n">
-        <v>6696827</v>
+        <v>6696795</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4562,10 +4562,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124288654</v>
+        <v>124288655</v>
       </c>
       <c r="B35" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4574,25 +4574,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555776</v>
+        <v>555733</v>
       </c>
       <c r="R35" t="n">
-        <v>6696789</v>
+        <v>6696827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124288656</v>
+        <v>124288654</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>91457</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4982,25 +4982,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555769</v>
+        <v>555776</v>
       </c>
       <c r="R39" t="n">
-        <v>6696795</v>
+        <v>6696789</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -4664,7 +4664,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288645</v>
+        <v>124288646</v>
       </c>
       <c r="B36" t="n">
         <v>91012</v>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555769</v>
+        <v>555732</v>
       </c>
       <c r="R36" t="n">
-        <v>6696795</v>
+        <v>6696815</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288646</v>
+        <v>124288654</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4880,25 +4880,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555732</v>
+        <v>555776</v>
       </c>
       <c r="R38" t="n">
-        <v>6696815</v>
+        <v>6696789</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124288654</v>
+        <v>124288645</v>
       </c>
       <c r="B39" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4982,25 +4982,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555776</v>
+        <v>555769</v>
       </c>
       <c r="R39" t="n">
-        <v>6696789</v>
+        <v>6696795</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>129080492</v>
       </c>
       <c r="B40" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>129080494</v>
       </c>
       <c r="B42" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91732</v>
+        <v>91735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>129080497</v>
       </c>
       <c r="B46" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>129080521</v>
       </c>
       <c r="B47" t="n">
-        <v>86862</v>
+        <v>86865</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129080496</v>
+        <v>129080504</v>
       </c>
       <c r="B50" t="n">
-        <v>91520</v>
+        <v>91978</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555738</v>
+        <v>555776</v>
       </c>
       <c r="R50" t="n">
-        <v>6696882</v>
+        <v>6696786</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129080504</v>
+        <v>129080496</v>
       </c>
       <c r="B51" t="n">
-        <v>91975</v>
+        <v>91523</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555776</v>
+        <v>555738</v>
       </c>
       <c r="R51" t="n">
-        <v>6696786</v>
+        <v>6696882</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080508</v>
+        <v>129080499</v>
       </c>
       <c r="B52" t="n">
-        <v>91805</v>
+        <v>57883</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6270,34 +6270,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555770</v>
+        <v>555799</v>
       </c>
       <c r="R52" t="n">
-        <v>6696857</v>
+        <v>6696875</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6356,38 +6361,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080499</v>
+        <v>129080516</v>
       </c>
       <c r="B53" t="n">
-        <v>57883</v>
+        <v>98656</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6396,10 +6405,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555799</v>
+        <v>555717</v>
       </c>
       <c r="R53" t="n">
-        <v>6696875</v>
+        <v>6696796</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6458,10 +6467,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080516</v>
+        <v>129080514</v>
       </c>
       <c r="B54" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6497,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6502,10 +6511,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555717</v>
+        <v>555713</v>
       </c>
       <c r="R54" t="n">
-        <v>6696796</v>
+        <v>6696791</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6564,54 +6573,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080514</v>
+        <v>129080508</v>
       </c>
       <c r="B55" t="n">
-        <v>98651</v>
+        <v>91808</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555713</v>
+        <v>555770</v>
       </c>
       <c r="R55" t="n">
-        <v>6696791</v>
+        <v>6696857</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6673,7 +6673,7 @@
         <v>129080509</v>
       </c>
       <c r="B56" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>129080510</v>
       </c>
       <c r="B57" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>129080493</v>
       </c>
       <c r="B58" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>129080518</v>
       </c>
       <c r="B61" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>129080506</v>
       </c>
       <c r="B62" t="n">
-        <v>92143</v>
+        <v>92148</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>129080515</v>
       </c>
       <c r="B63" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>129080492</v>
       </c>
       <c r="B40" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>129080494</v>
       </c>
       <c r="B42" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91735</v>
+        <v>91738</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>129080497</v>
       </c>
       <c r="B46" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>129080521</v>
       </c>
       <c r="B47" t="n">
-        <v>86865</v>
+        <v>86868</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>129080504</v>
       </c>
       <c r="B50" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>129080496</v>
       </c>
       <c r="B51" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080499</v>
+        <v>129080508</v>
       </c>
       <c r="B52" t="n">
-        <v>57883</v>
+        <v>91811</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6270,39 +6270,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555799</v>
+        <v>555770</v>
       </c>
       <c r="R52" t="n">
-        <v>6696875</v>
+        <v>6696857</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6361,54 +6356,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080516</v>
+        <v>129080509</v>
       </c>
       <c r="B53" t="n">
-        <v>98656</v>
+        <v>91811</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555717</v>
+        <v>555776</v>
       </c>
       <c r="R53" t="n">
-        <v>6696796</v>
+        <v>6696866</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6467,42 +6453,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080514</v>
+        <v>129080499</v>
       </c>
       <c r="B54" t="n">
-        <v>98656</v>
+        <v>57883</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6511,10 +6493,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555713</v>
+        <v>555799</v>
       </c>
       <c r="R54" t="n">
-        <v>6696791</v>
+        <v>6696875</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6573,45 +6555,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080508</v>
+        <v>129080516</v>
       </c>
       <c r="B55" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555770</v>
+        <v>555717</v>
       </c>
       <c r="R55" t="n">
-        <v>6696857</v>
+        <v>6696796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6670,45 +6661,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080509</v>
+        <v>129080514</v>
       </c>
       <c r="B56" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555776</v>
+        <v>555713</v>
       </c>
       <c r="R56" t="n">
-        <v>6696866</v>
+        <v>6696791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6770,7 +6770,7 @@
         <v>129080510</v>
       </c>
       <c r="B57" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>129080493</v>
       </c>
       <c r="B58" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>129080518</v>
       </c>
       <c r="B61" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7270,10 +7270,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080506</v>
+        <v>129080515</v>
       </c>
       <c r="B62" t="n">
-        <v>92148</v>
+        <v>98659</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7281,34 +7281,43 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555779</v>
+        <v>555725</v>
       </c>
       <c r="R62" t="n">
-        <v>6696887</v>
+        <v>6696807</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,10 +7376,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080515</v>
+        <v>129080506</v>
       </c>
       <c r="B63" t="n">
-        <v>98656</v>
+        <v>92151</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7378,43 +7387,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555725</v>
+        <v>555779</v>
       </c>
       <c r="R63" t="n">
-        <v>6696807</v>
+        <v>6696887</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5663,45 +5663,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080497</v>
+        <v>129080521</v>
       </c>
       <c r="B46" t="n">
-        <v>91526</v>
+        <v>86868</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555735</v>
+        <v>555798</v>
       </c>
       <c r="R46" t="n">
-        <v>6696818</v>
+        <v>6696849</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5736,12 +5739,18 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ingen reaktion med KOH.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5760,48 +5769,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080521</v>
+        <v>129080497</v>
       </c>
       <c r="B47" t="n">
-        <v>86868</v>
+        <v>91526</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>442</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555798</v>
+        <v>555735</v>
       </c>
       <c r="R47" t="n">
-        <v>6696849</v>
+        <v>6696818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5836,18 +5842,12 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ingen reaktion med KOH.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080508</v>
+        <v>129080499</v>
       </c>
       <c r="B52" t="n">
-        <v>91811</v>
+        <v>57883</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6270,34 +6270,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555770</v>
+        <v>555799</v>
       </c>
       <c r="R52" t="n">
-        <v>6696857</v>
+        <v>6696875</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6356,7 +6361,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080509</v>
+        <v>129080508</v>
       </c>
       <c r="B53" t="n">
         <v>91811</v>
@@ -6391,10 +6396,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555776</v>
+        <v>555770</v>
       </c>
       <c r="R53" t="n">
-        <v>6696866</v>
+        <v>6696857</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6453,10 +6458,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080499</v>
+        <v>129080509</v>
       </c>
       <c r="B54" t="n">
-        <v>57883</v>
+        <v>91811</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6464,39 +6469,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555799</v>
+        <v>555776</v>
       </c>
       <c r="R54" t="n">
-        <v>6696875</v>
+        <v>6696866</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7164,54 +7164,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080518</v>
+        <v>129080506</v>
       </c>
       <c r="B61" t="n">
-        <v>92855</v>
+        <v>92151</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5964</v>
+        <v>483</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555789</v>
+        <v>555779</v>
       </c>
       <c r="R61" t="n">
-        <v>6696889</v>
+        <v>6696887</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7270,42 +7261,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080515</v>
+        <v>129080518</v>
       </c>
       <c r="B62" t="n">
-        <v>98659</v>
+        <v>92855</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7314,10 +7305,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555725</v>
+        <v>555789</v>
       </c>
       <c r="R62" t="n">
-        <v>6696807</v>
+        <v>6696889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7376,10 +7367,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080506</v>
+        <v>129080515</v>
       </c>
       <c r="B63" t="n">
-        <v>92151</v>
+        <v>98659</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7387,34 +7378,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555779</v>
+        <v>555725</v>
       </c>
       <c r="R63" t="n">
-        <v>6696887</v>
+        <v>6696807</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -6767,10 +6767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080510</v>
+        <v>129080493</v>
       </c>
       <c r="B57" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6778,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555735</v>
+        <v>555776</v>
       </c>
       <c r="R57" t="n">
-        <v>6696835</v>
+        <v>6696784</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080493</v>
+        <v>129080510</v>
       </c>
       <c r="B58" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555776</v>
+        <v>555735</v>
       </c>
       <c r="R58" t="n">
-        <v>6696784</v>
+        <v>6696835</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5663,48 +5663,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080521</v>
+        <v>129080497</v>
       </c>
       <c r="B46" t="n">
-        <v>86868</v>
+        <v>91526</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>442</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555798</v>
+        <v>555735</v>
       </c>
       <c r="R46" t="n">
-        <v>6696849</v>
+        <v>6696818</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5739,18 +5736,12 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ingen reaktion med KOH.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5769,45 +5760,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080497</v>
+        <v>129080521</v>
       </c>
       <c r="B47" t="n">
-        <v>91526</v>
+        <v>86868</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555735</v>
+        <v>555798</v>
       </c>
       <c r="R47" t="n">
-        <v>6696818</v>
+        <v>6696849</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5842,12 +5836,18 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ingen reaktion med KOH.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129080504</v>
+        <v>129080496</v>
       </c>
       <c r="B50" t="n">
-        <v>91981</v>
+        <v>91526</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555776</v>
+        <v>555738</v>
       </c>
       <c r="R50" t="n">
-        <v>6696786</v>
+        <v>6696882</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129080496</v>
+        <v>129080504</v>
       </c>
       <c r="B51" t="n">
-        <v>91526</v>
+        <v>91981</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555738</v>
+        <v>555776</v>
       </c>
       <c r="R51" t="n">
-        <v>6696882</v>
+        <v>6696786</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080499</v>
+        <v>129080508</v>
       </c>
       <c r="B52" t="n">
-        <v>57883</v>
+        <v>91811</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6270,39 +6270,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555799</v>
+        <v>555770</v>
       </c>
       <c r="R52" t="n">
-        <v>6696875</v>
+        <v>6696857</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6361,7 +6356,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080508</v>
+        <v>129080509</v>
       </c>
       <c r="B53" t="n">
         <v>91811</v>
@@ -6396,10 +6391,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555770</v>
+        <v>555776</v>
       </c>
       <c r="R53" t="n">
-        <v>6696857</v>
+        <v>6696866</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6458,10 +6453,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080509</v>
+        <v>129080499</v>
       </c>
       <c r="B54" t="n">
-        <v>91811</v>
+        <v>57883</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6469,34 +6464,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555776</v>
+        <v>555799</v>
       </c>
       <c r="R54" t="n">
-        <v>6696866</v>
+        <v>6696875</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>129080492</v>
       </c>
       <c r="B40" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>129080494</v>
       </c>
       <c r="B42" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91738</v>
+        <v>91745</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5663,45 +5663,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080497</v>
+        <v>129080521</v>
       </c>
       <c r="B46" t="n">
-        <v>91526</v>
+        <v>86872</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555735</v>
+        <v>555798</v>
       </c>
       <c r="R46" t="n">
-        <v>6696818</v>
+        <v>6696849</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5736,12 +5739,18 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ingen reaktion med KOH.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5760,48 +5769,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080521</v>
+        <v>129080497</v>
       </c>
       <c r="B47" t="n">
-        <v>86868</v>
+        <v>91533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>442</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555798</v>
+        <v>555735</v>
       </c>
       <c r="R47" t="n">
-        <v>6696849</v>
+        <v>6696818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5836,18 +5842,12 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ingen reaktion med KOH.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>129080498</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129080496</v>
+        <v>129080504</v>
       </c>
       <c r="B50" t="n">
-        <v>91526</v>
+        <v>91988</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555738</v>
+        <v>555776</v>
       </c>
       <c r="R50" t="n">
-        <v>6696882</v>
+        <v>6696786</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129080504</v>
+        <v>129080496</v>
       </c>
       <c r="B51" t="n">
-        <v>91981</v>
+        <v>91533</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555776</v>
+        <v>555738</v>
       </c>
       <c r="R51" t="n">
-        <v>6696786</v>
+        <v>6696882</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6259,45 +6259,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080508</v>
+        <v>129080516</v>
       </c>
       <c r="B52" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555770</v>
+        <v>555717</v>
       </c>
       <c r="R52" t="n">
-        <v>6696857</v>
+        <v>6696796</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6356,45 +6365,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080509</v>
+        <v>129080514</v>
       </c>
       <c r="B53" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555776</v>
+        <v>555713</v>
       </c>
       <c r="R53" t="n">
-        <v>6696866</v>
+        <v>6696791</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6453,10 +6471,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080499</v>
+        <v>129080508</v>
       </c>
       <c r="B54" t="n">
-        <v>57883</v>
+        <v>91818</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6464,39 +6482,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555799</v>
+        <v>555770</v>
       </c>
       <c r="R54" t="n">
-        <v>6696875</v>
+        <v>6696857</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6555,54 +6568,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080516</v>
+        <v>129080509</v>
       </c>
       <c r="B55" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555717</v>
+        <v>555776</v>
       </c>
       <c r="R55" t="n">
-        <v>6696796</v>
+        <v>6696866</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6661,42 +6665,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080514</v>
+        <v>129080499</v>
       </c>
       <c r="B56" t="n">
-        <v>98659</v>
+        <v>57885</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555713</v>
+        <v>555799</v>
       </c>
       <c r="R56" t="n">
-        <v>6696791</v>
+        <v>6696875</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6770,7 +6770,7 @@
         <v>129080493</v>
       </c>
       <c r="B57" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>129080510</v>
       </c>
       <c r="B58" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7164,45 +7164,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080506</v>
+        <v>129080518</v>
       </c>
       <c r="B61" t="n">
-        <v>92151</v>
+        <v>92862</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>483</v>
+        <v>5964</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555779</v>
+        <v>555789</v>
       </c>
       <c r="R61" t="n">
-        <v>6696887</v>
+        <v>6696889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7261,54 +7270,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080518</v>
+        <v>129080506</v>
       </c>
       <c r="B62" t="n">
-        <v>92855</v>
+        <v>92158</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5964</v>
+        <v>483</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555789</v>
+        <v>555779</v>
       </c>
       <c r="R62" t="n">
-        <v>6696889</v>
+        <v>6696887</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7370,7 +7370,7 @@
         <v>129080515</v>
       </c>
       <c r="B63" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -7164,54 +7164,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080518</v>
+        <v>129080506</v>
       </c>
       <c r="B61" t="n">
-        <v>92862</v>
+        <v>92158</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5964</v>
+        <v>483</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555789</v>
+        <v>555779</v>
       </c>
       <c r="R61" t="n">
-        <v>6696889</v>
+        <v>6696887</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7270,45 +7261,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080506</v>
+        <v>129080518</v>
       </c>
       <c r="B62" t="n">
-        <v>92158</v>
+        <v>92862</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>483</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555779</v>
+        <v>555789</v>
       </c>
       <c r="R62" t="n">
-        <v>6696887</v>
+        <v>6696889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>129080492</v>
       </c>
       <c r="B40" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>129080494</v>
       </c>
       <c r="B42" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91745</v>
+        <v>91752</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>129080521</v>
       </c>
       <c r="B46" t="n">
-        <v>86872</v>
+        <v>86879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>129080497</v>
       </c>
       <c r="B47" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>129080504</v>
       </c>
       <c r="B50" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>129080496</v>
       </c>
       <c r="B51" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>129080516</v>
       </c>
       <c r="B52" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>129080514</v>
       </c>
       <c r="B53" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6471,10 +6471,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080508</v>
+        <v>129080499</v>
       </c>
       <c r="B54" t="n">
-        <v>91818</v>
+        <v>57885</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6482,34 +6482,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555770</v>
+        <v>555799</v>
       </c>
       <c r="R54" t="n">
-        <v>6696857</v>
+        <v>6696875</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6568,10 +6573,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080509</v>
+        <v>129080508</v>
       </c>
       <c r="B55" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6603,10 +6608,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555776</v>
+        <v>555770</v>
       </c>
       <c r="R55" t="n">
-        <v>6696866</v>
+        <v>6696857</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6665,10 +6670,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080499</v>
+        <v>129080509</v>
       </c>
       <c r="B56" t="n">
-        <v>57885</v>
+        <v>91825</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6676,39 +6681,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555799</v>
+        <v>555776</v>
       </c>
       <c r="R56" t="n">
-        <v>6696875</v>
+        <v>6696866</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080493</v>
+        <v>129080510</v>
       </c>
       <c r="B57" t="n">
-        <v>91533</v>
+        <v>91825</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6778,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555776</v>
+        <v>555735</v>
       </c>
       <c r="R57" t="n">
-        <v>6696784</v>
+        <v>6696835</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080510</v>
+        <v>129080493</v>
       </c>
       <c r="B58" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555735</v>
+        <v>555776</v>
       </c>
       <c r="R58" t="n">
-        <v>6696835</v>
+        <v>6696784</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7164,45 +7164,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080506</v>
+        <v>129080518</v>
       </c>
       <c r="B61" t="n">
-        <v>92158</v>
+        <v>92869</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>483</v>
+        <v>5964</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555779</v>
+        <v>555789</v>
       </c>
       <c r="R61" t="n">
-        <v>6696887</v>
+        <v>6696889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7261,42 +7270,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080518</v>
+        <v>129080515</v>
       </c>
       <c r="B62" t="n">
-        <v>92862</v>
+        <v>98676</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7305,10 +7314,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555789</v>
+        <v>555725</v>
       </c>
       <c r="R62" t="n">
-        <v>6696889</v>
+        <v>6696807</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,10 +7376,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080515</v>
+        <v>129080506</v>
       </c>
       <c r="B63" t="n">
-        <v>98669</v>
+        <v>92165</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7378,43 +7387,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555725</v>
+        <v>555779</v>
       </c>
       <c r="R63" t="n">
-        <v>6696807</v>
+        <v>6696887</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>129080492</v>
       </c>
       <c r="B40" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>129080494</v>
       </c>
       <c r="B42" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91752</v>
+        <v>91754</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5663,48 +5663,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080521</v>
+        <v>129080497</v>
       </c>
       <c r="B46" t="n">
-        <v>86879</v>
+        <v>91542</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>442</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555798</v>
+        <v>555735</v>
       </c>
       <c r="R46" t="n">
-        <v>6696849</v>
+        <v>6696818</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5739,18 +5736,12 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ingen reaktion med KOH.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5769,45 +5760,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080497</v>
+        <v>129080521</v>
       </c>
       <c r="B47" t="n">
-        <v>91540</v>
+        <v>86881</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555735</v>
+        <v>555798</v>
       </c>
       <c r="R47" t="n">
-        <v>6696818</v>
+        <v>6696849</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5842,12 +5836,18 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ingen reaktion med KOH.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>129080498</v>
       </c>
       <c r="B49" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>129080504</v>
       </c>
       <c r="B50" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>129080496</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6259,54 +6259,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080516</v>
+        <v>129080508</v>
       </c>
       <c r="B52" t="n">
-        <v>98676</v>
+        <v>91827</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555717</v>
+        <v>555770</v>
       </c>
       <c r="R52" t="n">
-        <v>6696796</v>
+        <v>6696857</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6365,54 +6356,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080514</v>
+        <v>129080509</v>
       </c>
       <c r="B53" t="n">
-        <v>98676</v>
+        <v>91827</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555713</v>
+        <v>555776</v>
       </c>
       <c r="R53" t="n">
-        <v>6696791</v>
+        <v>6696866</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6471,38 +6453,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080499</v>
+        <v>129080516</v>
       </c>
       <c r="B54" t="n">
-        <v>57885</v>
+        <v>98678</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6511,10 +6497,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555799</v>
+        <v>555717</v>
       </c>
       <c r="R54" t="n">
-        <v>6696875</v>
+        <v>6696796</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6573,45 +6559,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080508</v>
+        <v>129080514</v>
       </c>
       <c r="B55" t="n">
-        <v>91825</v>
+        <v>98678</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555770</v>
+        <v>555713</v>
       </c>
       <c r="R55" t="n">
-        <v>6696857</v>
+        <v>6696791</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6670,10 +6665,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080509</v>
+        <v>129080499</v>
       </c>
       <c r="B56" t="n">
-        <v>91825</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6681,34 +6676,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555776</v>
+        <v>555799</v>
       </c>
       <c r="R56" t="n">
-        <v>6696866</v>
+        <v>6696875</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6770,7 +6770,7 @@
         <v>129080510</v>
       </c>
       <c r="B57" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>129080493</v>
       </c>
       <c r="B58" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7164,54 +7164,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080518</v>
+        <v>129080506</v>
       </c>
       <c r="B61" t="n">
-        <v>92869</v>
+        <v>92167</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5964</v>
+        <v>483</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555789</v>
+        <v>555779</v>
       </c>
       <c r="R61" t="n">
-        <v>6696889</v>
+        <v>6696887</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7270,42 +7261,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080515</v>
+        <v>129080518</v>
       </c>
       <c r="B62" t="n">
-        <v>98676</v>
+        <v>92871</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7314,10 +7305,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555725</v>
+        <v>555789</v>
       </c>
       <c r="R62" t="n">
-        <v>6696807</v>
+        <v>6696889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7376,10 +7367,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080506</v>
+        <v>129080515</v>
       </c>
       <c r="B63" t="n">
-        <v>92165</v>
+        <v>98678</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7387,34 +7378,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555779</v>
+        <v>555725</v>
       </c>
       <c r="R63" t="n">
-        <v>6696887</v>
+        <v>6696807</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -6065,32 +6065,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129080504</v>
+        <v>129080496</v>
       </c>
       <c r="B50" t="n">
-        <v>91997</v>
+        <v>91542</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555776</v>
+        <v>555738</v>
       </c>
       <c r="R50" t="n">
-        <v>6696786</v>
+        <v>6696882</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129080496</v>
+        <v>129080504</v>
       </c>
       <c r="B51" t="n">
-        <v>91542</v>
+        <v>91997</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555738</v>
+        <v>555776</v>
       </c>
       <c r="R51" t="n">
-        <v>6696882</v>
+        <v>6696786</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080508</v>
+        <v>129080499</v>
       </c>
       <c r="B52" t="n">
-        <v>91827</v>
+        <v>57887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6270,34 +6270,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555770</v>
+        <v>555799</v>
       </c>
       <c r="R52" t="n">
-        <v>6696857</v>
+        <v>6696875</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6356,7 +6361,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080509</v>
+        <v>129080508</v>
       </c>
       <c r="B53" t="n">
         <v>91827</v>
@@ -6391,10 +6396,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555776</v>
+        <v>555770</v>
       </c>
       <c r="R53" t="n">
-        <v>6696866</v>
+        <v>6696857</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6453,54 +6458,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080516</v>
+        <v>129080509</v>
       </c>
       <c r="B54" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555717</v>
+        <v>555776</v>
       </c>
       <c r="R54" t="n">
-        <v>6696796</v>
+        <v>6696866</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6559,7 +6555,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080514</v>
+        <v>129080516</v>
       </c>
       <c r="B55" t="n">
         <v>98678</v>
@@ -6589,7 +6585,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6603,10 +6599,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555713</v>
+        <v>555717</v>
       </c>
       <c r="R55" t="n">
-        <v>6696791</v>
+        <v>6696796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6665,38 +6661,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080499</v>
+        <v>129080514</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>98678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555799</v>
+        <v>555713</v>
       </c>
       <c r="R56" t="n">
-        <v>6696875</v>
+        <v>6696791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080510</v>
+        <v>129080493</v>
       </c>
       <c r="B57" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6778,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555735</v>
+        <v>555776</v>
       </c>
       <c r="R57" t="n">
-        <v>6696835</v>
+        <v>6696784</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080493</v>
+        <v>129080510</v>
       </c>
       <c r="B58" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555776</v>
+        <v>555735</v>
       </c>
       <c r="R58" t="n">
-        <v>6696784</v>
+        <v>6696835</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -6259,38 +6259,42 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080499</v>
+        <v>129080516</v>
       </c>
       <c r="B52" t="n">
-        <v>57887</v>
+        <v>98678</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6299,10 +6303,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555799</v>
+        <v>555717</v>
       </c>
       <c r="R52" t="n">
-        <v>6696875</v>
+        <v>6696796</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6361,45 +6365,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080508</v>
+        <v>129080514</v>
       </c>
       <c r="B53" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555770</v>
+        <v>555713</v>
       </c>
       <c r="R53" t="n">
-        <v>6696857</v>
+        <v>6696791</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6458,10 +6471,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080509</v>
+        <v>129080499</v>
       </c>
       <c r="B54" t="n">
-        <v>91827</v>
+        <v>57887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6469,34 +6482,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555776</v>
+        <v>555799</v>
       </c>
       <c r="R54" t="n">
-        <v>6696866</v>
+        <v>6696875</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6555,54 +6573,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080516</v>
+        <v>129080508</v>
       </c>
       <c r="B55" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555717</v>
+        <v>555770</v>
       </c>
       <c r="R55" t="n">
-        <v>6696796</v>
+        <v>6696857</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6661,54 +6670,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080514</v>
+        <v>129080509</v>
       </c>
       <c r="B56" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555713</v>
+        <v>555776</v>
       </c>
       <c r="R56" t="n">
-        <v>6696791</v>
+        <v>6696866</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7164,10 +7164,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080506</v>
+        <v>129080515</v>
       </c>
       <c r="B61" t="n">
-        <v>92167</v>
+        <v>98678</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7175,34 +7175,43 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555779</v>
+        <v>555725</v>
       </c>
       <c r="R61" t="n">
-        <v>6696887</v>
+        <v>6696807</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7261,54 +7270,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080518</v>
+        <v>129080506</v>
       </c>
       <c r="B62" t="n">
-        <v>92871</v>
+        <v>92167</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5964</v>
+        <v>483</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555789</v>
+        <v>555779</v>
       </c>
       <c r="R62" t="n">
-        <v>6696889</v>
+        <v>6696887</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,42 +7367,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080515</v>
+        <v>129080518</v>
       </c>
       <c r="B63" t="n">
-        <v>98678</v>
+        <v>92871</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555725</v>
+        <v>555789</v>
       </c>
       <c r="R63" t="n">
-        <v>6696807</v>
+        <v>6696889</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>129080492</v>
       </c>
       <c r="B40" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>129080494</v>
       </c>
       <c r="B42" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91754</v>
+        <v>91763</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>129080497</v>
       </c>
       <c r="B46" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>129080521</v>
       </c>
       <c r="B47" t="n">
-        <v>86881</v>
+        <v>86882</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>129080496</v>
       </c>
       <c r="B50" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>129080504</v>
       </c>
       <c r="B51" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6259,54 +6259,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080516</v>
+        <v>129080508</v>
       </c>
       <c r="B52" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555717</v>
+        <v>555770</v>
       </c>
       <c r="R52" t="n">
-        <v>6696796</v>
+        <v>6696857</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6365,54 +6356,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080514</v>
+        <v>129080509</v>
       </c>
       <c r="B53" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555713</v>
+        <v>555776</v>
       </c>
       <c r="R53" t="n">
-        <v>6696791</v>
+        <v>6696866</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6573,45 +6555,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080508</v>
+        <v>129080516</v>
       </c>
       <c r="B55" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555770</v>
+        <v>555717</v>
       </c>
       <c r="R55" t="n">
-        <v>6696857</v>
+        <v>6696796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6670,45 +6661,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080509</v>
+        <v>129080514</v>
       </c>
       <c r="B56" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555776</v>
+        <v>555713</v>
       </c>
       <c r="R56" t="n">
-        <v>6696866</v>
+        <v>6696791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080493</v>
+        <v>129080510</v>
       </c>
       <c r="B57" t="n">
-        <v>91542</v>
+        <v>91837</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6778,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555776</v>
+        <v>555735</v>
       </c>
       <c r="R57" t="n">
-        <v>6696784</v>
+        <v>6696835</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080510</v>
+        <v>129080493</v>
       </c>
       <c r="B58" t="n">
-        <v>91827</v>
+        <v>91540</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555735</v>
+        <v>555776</v>
       </c>
       <c r="R58" t="n">
-        <v>6696835</v>
+        <v>6696784</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>129080515</v>
       </c>
       <c r="B61" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>129080506</v>
       </c>
       <c r="B62" t="n">
-        <v>92167</v>
+        <v>92182</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>129080518</v>
       </c>
       <c r="B63" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91763</v>
+        <v>91764</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>129080504</v>
       </c>
       <c r="B51" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>129080508</v>
       </c>
       <c r="B52" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>129080509</v>
       </c>
       <c r="B53" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080516</v>
+        <v>129080514</v>
       </c>
       <c r="B55" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555717</v>
+        <v>555713</v>
       </c>
       <c r="R55" t="n">
-        <v>6696796</v>
+        <v>6696791</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6661,10 +6661,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080514</v>
+        <v>129080516</v>
       </c>
       <c r="B56" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555713</v>
+        <v>555717</v>
       </c>
       <c r="R56" t="n">
-        <v>6696791</v>
+        <v>6696796</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6770,7 +6770,7 @@
         <v>129080510</v>
       </c>
       <c r="B57" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080515</v>
+        <v>129080506</v>
       </c>
       <c r="B61" t="n">
-        <v>98704</v>
+        <v>92183</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7175,43 +7175,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555725</v>
+        <v>555779</v>
       </c>
       <c r="R61" t="n">
-        <v>6696807</v>
+        <v>6696887</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7270,45 +7261,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080506</v>
+        <v>129080518</v>
       </c>
       <c r="B62" t="n">
-        <v>92182</v>
+        <v>92858</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>483</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555779</v>
+        <v>555789</v>
       </c>
       <c r="R62" t="n">
-        <v>6696887</v>
+        <v>6696889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,42 +7367,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080518</v>
+        <v>129080515</v>
       </c>
       <c r="B63" t="n">
-        <v>92857</v>
+        <v>98705</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555789</v>
+        <v>555725</v>
       </c>
       <c r="R63" t="n">
-        <v>6696889</v>
+        <v>6696807</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5663,45 +5663,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080497</v>
+        <v>129080521</v>
       </c>
       <c r="B46" t="n">
-        <v>91540</v>
+        <v>86882</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555735</v>
+        <v>555798</v>
       </c>
       <c r="R46" t="n">
-        <v>6696818</v>
+        <v>6696849</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5736,12 +5739,18 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ingen reaktion med KOH.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5760,48 +5769,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080521</v>
+        <v>129080497</v>
       </c>
       <c r="B47" t="n">
-        <v>86882</v>
+        <v>91540</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>442</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555798</v>
+        <v>555735</v>
       </c>
       <c r="R47" t="n">
-        <v>6696849</v>
+        <v>6696818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5836,18 +5842,12 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ingen reaktion med KOH.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080514</v>
+        <v>129080516</v>
       </c>
       <c r="B55" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555713</v>
+        <v>555717</v>
       </c>
       <c r="R55" t="n">
-        <v>6696791</v>
+        <v>6696796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6661,10 +6661,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080516</v>
+        <v>129080514</v>
       </c>
       <c r="B56" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555717</v>
+        <v>555713</v>
       </c>
       <c r="R56" t="n">
-        <v>6696796</v>
+        <v>6696791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080510</v>
+        <v>129080493</v>
       </c>
       <c r="B57" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6778,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555735</v>
+        <v>555776</v>
       </c>
       <c r="R57" t="n">
-        <v>6696835</v>
+        <v>6696784</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080493</v>
+        <v>129080510</v>
       </c>
       <c r="B58" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555776</v>
+        <v>555735</v>
       </c>
       <c r="R58" t="n">
-        <v>6696784</v>
+        <v>6696835</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>129080515</v>
       </c>
       <c r="B63" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>129080492</v>
       </c>
       <c r="B40" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>129080494</v>
       </c>
       <c r="B42" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91764</v>
+        <v>91767</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5663,48 +5663,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080521</v>
+        <v>129080497</v>
       </c>
       <c r="B46" t="n">
-        <v>86882</v>
+        <v>91543</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>442</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555798</v>
+        <v>555735</v>
       </c>
       <c r="R46" t="n">
-        <v>6696849</v>
+        <v>6696818</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5739,18 +5736,12 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ingen reaktion med KOH.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5769,45 +5760,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080497</v>
+        <v>129080521</v>
       </c>
       <c r="B47" t="n">
-        <v>91540</v>
+        <v>86885</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555735</v>
+        <v>555798</v>
       </c>
       <c r="R47" t="n">
-        <v>6696818</v>
+        <v>6696849</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5842,12 +5836,18 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ingen reaktion med KOH.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>129080496</v>
       </c>
       <c r="B50" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>129080504</v>
       </c>
       <c r="B51" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>129080508</v>
       </c>
       <c r="B52" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>129080509</v>
       </c>
       <c r="B53" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080516</v>
+        <v>129080514</v>
       </c>
       <c r="B55" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555717</v>
+        <v>555713</v>
       </c>
       <c r="R55" t="n">
-        <v>6696796</v>
+        <v>6696791</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6661,10 +6661,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080514</v>
+        <v>129080516</v>
       </c>
       <c r="B56" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555713</v>
+        <v>555717</v>
       </c>
       <c r="R56" t="n">
-        <v>6696791</v>
+        <v>6696796</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080493</v>
+        <v>129080510</v>
       </c>
       <c r="B57" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6778,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555776</v>
+        <v>555735</v>
       </c>
       <c r="R57" t="n">
-        <v>6696784</v>
+        <v>6696835</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080510</v>
+        <v>129080493</v>
       </c>
       <c r="B58" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555735</v>
+        <v>555776</v>
       </c>
       <c r="R58" t="n">
-        <v>6696835</v>
+        <v>6696784</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>129080506</v>
       </c>
       <c r="B61" t="n">
-        <v>92183</v>
+        <v>92186</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7261,42 +7261,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080518</v>
+        <v>129080515</v>
       </c>
       <c r="B62" t="n">
-        <v>92858</v>
+        <v>98710</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7305,10 +7305,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555789</v>
+        <v>555725</v>
       </c>
       <c r="R62" t="n">
-        <v>6696889</v>
+        <v>6696807</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,42 +7367,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080515</v>
+        <v>129080518</v>
       </c>
       <c r="B63" t="n">
-        <v>98706</v>
+        <v>92861</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555725</v>
+        <v>555789</v>
       </c>
       <c r="R63" t="n">
-        <v>6696807</v>
+        <v>6696889</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>129080492</v>
       </c>
       <c r="B40" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>129080494</v>
       </c>
       <c r="B42" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91767</v>
+        <v>91769</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>129080497</v>
       </c>
       <c r="B46" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>129080521</v>
       </c>
       <c r="B47" t="n">
-        <v>86885</v>
+        <v>86887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>129080496</v>
       </c>
       <c r="B50" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>129080504</v>
       </c>
       <c r="B51" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080508</v>
+        <v>129080499</v>
       </c>
       <c r="B52" t="n">
-        <v>91841</v>
+        <v>57887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6270,34 +6270,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555770</v>
+        <v>555799</v>
       </c>
       <c r="R52" t="n">
-        <v>6696857</v>
+        <v>6696875</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6356,10 +6361,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080509</v>
+        <v>129080508</v>
       </c>
       <c r="B53" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6391,10 +6396,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555776</v>
+        <v>555770</v>
       </c>
       <c r="R53" t="n">
-        <v>6696866</v>
+        <v>6696857</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6453,10 +6458,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080499</v>
+        <v>129080509</v>
       </c>
       <c r="B54" t="n">
-        <v>57887</v>
+        <v>91843</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6464,39 +6469,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555799</v>
+        <v>555776</v>
       </c>
       <c r="R54" t="n">
-        <v>6696875</v>
+        <v>6696866</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6558,7 +6558,7 @@
         <v>129080514</v>
       </c>
       <c r="B55" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>129080516</v>
       </c>
       <c r="B56" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>129080510</v>
       </c>
       <c r="B57" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>129080493</v>
       </c>
       <c r="B58" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>129080506</v>
       </c>
       <c r="B61" t="n">
-        <v>92186</v>
+        <v>92188</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>129080515</v>
       </c>
       <c r="B62" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>129080518</v>
       </c>
       <c r="B63" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>129080492</v>
       </c>
       <c r="B40" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>129080494</v>
       </c>
       <c r="B42" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91769</v>
+        <v>91773</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>129080497</v>
       </c>
       <c r="B46" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>129080521</v>
       </c>
       <c r="B47" t="n">
-        <v>86887</v>
+        <v>86891</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>129080496</v>
       </c>
       <c r="B50" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>129080504</v>
       </c>
       <c r="B51" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080499</v>
+        <v>129080508</v>
       </c>
       <c r="B52" t="n">
-        <v>57887</v>
+        <v>91847</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6270,39 +6270,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555799</v>
+        <v>555770</v>
       </c>
       <c r="R52" t="n">
-        <v>6696875</v>
+        <v>6696857</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6361,10 +6356,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080508</v>
+        <v>129080509</v>
       </c>
       <c r="B53" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6396,10 +6391,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555770</v>
+        <v>555776</v>
       </c>
       <c r="R53" t="n">
-        <v>6696857</v>
+        <v>6696866</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6458,10 +6453,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080509</v>
+        <v>129080499</v>
       </c>
       <c r="B54" t="n">
-        <v>91843</v>
+        <v>57887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6469,34 +6464,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555776</v>
+        <v>555799</v>
       </c>
       <c r="R54" t="n">
-        <v>6696866</v>
+        <v>6696875</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080514</v>
+        <v>129080516</v>
       </c>
       <c r="B55" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555713</v>
+        <v>555717</v>
       </c>
       <c r="R55" t="n">
-        <v>6696791</v>
+        <v>6696796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6661,10 +6661,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080516</v>
+        <v>129080514</v>
       </c>
       <c r="B56" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555717</v>
+        <v>555713</v>
       </c>
       <c r="R56" t="n">
-        <v>6696796</v>
+        <v>6696791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080510</v>
+        <v>129080493</v>
       </c>
       <c r="B57" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6778,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555735</v>
+        <v>555776</v>
       </c>
       <c r="R57" t="n">
-        <v>6696835</v>
+        <v>6696784</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080493</v>
+        <v>129080510</v>
       </c>
       <c r="B58" t="n">
-        <v>91545</v>
+        <v>91847</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555776</v>
+        <v>555735</v>
       </c>
       <c r="R58" t="n">
-        <v>6696784</v>
+        <v>6696835</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>129080506</v>
       </c>
       <c r="B61" t="n">
-        <v>92188</v>
+        <v>92192</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7261,42 +7261,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080515</v>
+        <v>129080518</v>
       </c>
       <c r="B62" t="n">
-        <v>98712</v>
+        <v>92867</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7305,10 +7305,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555725</v>
+        <v>555789</v>
       </c>
       <c r="R62" t="n">
-        <v>6696807</v>
+        <v>6696889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,42 +7367,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080518</v>
+        <v>129080515</v>
       </c>
       <c r="B63" t="n">
-        <v>92863</v>
+        <v>98716</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555789</v>
+        <v>555725</v>
       </c>
       <c r="R63" t="n">
-        <v>6696889</v>
+        <v>6696807</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>129080492</v>
       </c>
       <c r="B40" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>129080494</v>
       </c>
       <c r="B42" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91773</v>
+        <v>91774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>129080497</v>
       </c>
       <c r="B46" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>129080521</v>
       </c>
       <c r="B47" t="n">
-        <v>86891</v>
+        <v>86892</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>129080496</v>
       </c>
       <c r="B50" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>129080504</v>
       </c>
       <c r="B51" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>129080508</v>
       </c>
       <c r="B52" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>129080509</v>
       </c>
       <c r="B53" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6453,38 +6453,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080499</v>
+        <v>129080516</v>
       </c>
       <c r="B54" t="n">
-        <v>57887</v>
+        <v>98724</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6493,10 +6497,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555799</v>
+        <v>555717</v>
       </c>
       <c r="R54" t="n">
-        <v>6696875</v>
+        <v>6696796</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6555,10 +6559,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080516</v>
+        <v>129080514</v>
       </c>
       <c r="B55" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6585,7 +6589,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6599,10 +6603,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555717</v>
+        <v>555713</v>
       </c>
       <c r="R55" t="n">
-        <v>6696796</v>
+        <v>6696791</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6661,42 +6665,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080514</v>
+        <v>129080499</v>
       </c>
       <c r="B56" t="n">
-        <v>98716</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555713</v>
+        <v>555799</v>
       </c>
       <c r="R56" t="n">
-        <v>6696791</v>
+        <v>6696875</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080493</v>
+        <v>129080510</v>
       </c>
       <c r="B57" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6778,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555776</v>
+        <v>555735</v>
       </c>
       <c r="R57" t="n">
-        <v>6696784</v>
+        <v>6696835</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080510</v>
+        <v>129080493</v>
       </c>
       <c r="B58" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555735</v>
+        <v>555776</v>
       </c>
       <c r="R58" t="n">
-        <v>6696835</v>
+        <v>6696784</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92843</v>
+        <v>92844</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>129080506</v>
       </c>
       <c r="B61" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>129080518</v>
       </c>
       <c r="B62" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>129080515</v>
       </c>
       <c r="B63" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -6065,32 +6065,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129080496</v>
+        <v>129080504</v>
       </c>
       <c r="B50" t="n">
-        <v>91550</v>
+        <v>92003</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555738</v>
+        <v>555776</v>
       </c>
       <c r="R50" t="n">
-        <v>6696882</v>
+        <v>6696786</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129080504</v>
+        <v>129080496</v>
       </c>
       <c r="B51" t="n">
-        <v>92003</v>
+        <v>91550</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555776</v>
+        <v>555738</v>
       </c>
       <c r="R51" t="n">
-        <v>6696786</v>
+        <v>6696882</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7164,10 +7164,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080506</v>
+        <v>129080515</v>
       </c>
       <c r="B61" t="n">
-        <v>92193</v>
+        <v>98724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7175,34 +7175,43 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555779</v>
+        <v>555725</v>
       </c>
       <c r="R61" t="n">
-        <v>6696887</v>
+        <v>6696807</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7261,54 +7270,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080518</v>
+        <v>129080506</v>
       </c>
       <c r="B62" t="n">
-        <v>92868</v>
+        <v>92193</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5964</v>
+        <v>483</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555789</v>
+        <v>555779</v>
       </c>
       <c r="R62" t="n">
-        <v>6696889</v>
+        <v>6696887</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,42 +7367,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080515</v>
+        <v>129080518</v>
       </c>
       <c r="B63" t="n">
-        <v>98724</v>
+        <v>92868</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555725</v>
+        <v>555789</v>
       </c>
       <c r="R63" t="n">
-        <v>6696807</v>
+        <v>6696889</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>129080492</v>
       </c>
       <c r="B40" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>129080494</v>
       </c>
       <c r="B42" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91774</v>
+        <v>91777</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>129080497</v>
       </c>
       <c r="B46" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129080504</v>
+        <v>129080496</v>
       </c>
       <c r="B50" t="n">
-        <v>92003</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555776</v>
+        <v>555738</v>
       </c>
       <c r="R50" t="n">
-        <v>6696786</v>
+        <v>6696882</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129080496</v>
+        <v>129080504</v>
       </c>
       <c r="B51" t="n">
-        <v>91550</v>
+        <v>92006</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555738</v>
+        <v>555776</v>
       </c>
       <c r="R51" t="n">
-        <v>6696882</v>
+        <v>6696786</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080508</v>
+        <v>129080499</v>
       </c>
       <c r="B52" t="n">
-        <v>91848</v>
+        <v>57887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6270,34 +6270,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555770</v>
+        <v>555799</v>
       </c>
       <c r="R52" t="n">
-        <v>6696857</v>
+        <v>6696875</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6356,45 +6361,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080509</v>
+        <v>129080516</v>
       </c>
       <c r="B53" t="n">
-        <v>91848</v>
+        <v>98727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555776</v>
+        <v>555717</v>
       </c>
       <c r="R53" t="n">
-        <v>6696866</v>
+        <v>6696796</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6453,10 +6467,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080516</v>
+        <v>129080514</v>
       </c>
       <c r="B54" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6483,7 +6497,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6497,10 +6511,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555717</v>
+        <v>555713</v>
       </c>
       <c r="R54" t="n">
-        <v>6696796</v>
+        <v>6696791</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6559,54 +6573,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080514</v>
+        <v>129080508</v>
       </c>
       <c r="B55" t="n">
-        <v>98724</v>
+        <v>91851</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555713</v>
+        <v>555770</v>
       </c>
       <c r="R55" t="n">
-        <v>6696791</v>
+        <v>6696857</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6665,10 +6670,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080499</v>
+        <v>129080509</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>91851</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6676,39 +6681,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555799</v>
+        <v>555776</v>
       </c>
       <c r="R56" t="n">
-        <v>6696875</v>
+        <v>6696866</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080510</v>
+        <v>129080493</v>
       </c>
       <c r="B57" t="n">
-        <v>91848</v>
+        <v>91553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6778,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555735</v>
+        <v>555776</v>
       </c>
       <c r="R57" t="n">
-        <v>6696835</v>
+        <v>6696784</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080493</v>
+        <v>129080510</v>
       </c>
       <c r="B58" t="n">
-        <v>91550</v>
+        <v>91851</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555776</v>
+        <v>555735</v>
       </c>
       <c r="R58" t="n">
-        <v>6696784</v>
+        <v>6696835</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92844</v>
+        <v>92847</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080515</v>
+        <v>129080506</v>
       </c>
       <c r="B61" t="n">
-        <v>98724</v>
+        <v>92196</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7175,43 +7175,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555725</v>
+        <v>555779</v>
       </c>
       <c r="R61" t="n">
-        <v>6696807</v>
+        <v>6696887</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7270,45 +7261,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080506</v>
+        <v>129080518</v>
       </c>
       <c r="B62" t="n">
-        <v>92193</v>
+        <v>92871</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>483</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555779</v>
+        <v>555789</v>
       </c>
       <c r="R62" t="n">
-        <v>6696887</v>
+        <v>6696889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,42 +7367,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080518</v>
+        <v>129080515</v>
       </c>
       <c r="B63" t="n">
-        <v>92868</v>
+        <v>98727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555789</v>
+        <v>555725</v>
       </c>
       <c r="R63" t="n">
-        <v>6696889</v>
+        <v>6696807</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -6361,54 +6361,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080516</v>
+        <v>129080508</v>
       </c>
       <c r="B53" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555717</v>
+        <v>555770</v>
       </c>
       <c r="R53" t="n">
-        <v>6696796</v>
+        <v>6696857</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6467,54 +6458,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080514</v>
+        <v>129080509</v>
       </c>
       <c r="B54" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555713</v>
+        <v>555776</v>
       </c>
       <c r="R54" t="n">
-        <v>6696791</v>
+        <v>6696866</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6573,45 +6555,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080508</v>
+        <v>129080516</v>
       </c>
       <c r="B55" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555770</v>
+        <v>555717</v>
       </c>
       <c r="R55" t="n">
-        <v>6696857</v>
+        <v>6696796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6670,45 +6661,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080509</v>
+        <v>129080514</v>
       </c>
       <c r="B56" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555776</v>
+        <v>555713</v>
       </c>
       <c r="R56" t="n">
-        <v>6696866</v>
+        <v>6696791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080493</v>
+        <v>129080510</v>
       </c>
       <c r="B57" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6778,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555776</v>
+        <v>555735</v>
       </c>
       <c r="R57" t="n">
-        <v>6696784</v>
+        <v>6696835</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080510</v>
+        <v>129080493</v>
       </c>
       <c r="B58" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555735</v>
+        <v>555776</v>
       </c>
       <c r="R58" t="n">
-        <v>6696835</v>
+        <v>6696784</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7261,42 +7261,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080518</v>
+        <v>129080515</v>
       </c>
       <c r="B62" t="n">
-        <v>92871</v>
+        <v>98727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7305,10 +7305,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555789</v>
+        <v>555725</v>
       </c>
       <c r="R62" t="n">
-        <v>6696889</v>
+        <v>6696807</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,42 +7367,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080515</v>
+        <v>129080518</v>
       </c>
       <c r="B63" t="n">
-        <v>98727</v>
+        <v>92871</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555725</v>
+        <v>555789</v>
       </c>
       <c r="R63" t="n">
-        <v>6696807</v>
+        <v>6696889</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5663,45 +5663,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080497</v>
+        <v>129080521</v>
       </c>
       <c r="B46" t="n">
-        <v>91553</v>
+        <v>86892</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555735</v>
+        <v>555798</v>
       </c>
       <c r="R46" t="n">
-        <v>6696818</v>
+        <v>6696849</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5736,12 +5739,18 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ingen reaktion med KOH.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5760,48 +5769,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080521</v>
+        <v>129080497</v>
       </c>
       <c r="B47" t="n">
-        <v>86892</v>
+        <v>91553</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>442</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555798</v>
+        <v>555735</v>
       </c>
       <c r="R47" t="n">
-        <v>6696849</v>
+        <v>6696818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5836,18 +5842,12 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ingen reaktion med KOH.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129080496</v>
+        <v>129080504</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>92006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555738</v>
+        <v>555776</v>
       </c>
       <c r="R50" t="n">
-        <v>6696882</v>
+        <v>6696786</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129080504</v>
+        <v>129080496</v>
       </c>
       <c r="B51" t="n">
-        <v>92006</v>
+        <v>91553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555776</v>
+        <v>555738</v>
       </c>
       <c r="R51" t="n">
-        <v>6696786</v>
+        <v>6696882</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6259,38 +6259,42 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080499</v>
+        <v>129080516</v>
       </c>
       <c r="B52" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6299,10 +6303,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555799</v>
+        <v>555717</v>
       </c>
       <c r="R52" t="n">
-        <v>6696875</v>
+        <v>6696796</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6361,45 +6365,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080508</v>
+        <v>129080514</v>
       </c>
       <c r="B53" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555770</v>
+        <v>555713</v>
       </c>
       <c r="R53" t="n">
-        <v>6696857</v>
+        <v>6696791</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6458,7 +6471,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080509</v>
+        <v>129080508</v>
       </c>
       <c r="B54" t="n">
         <v>91851</v>
@@ -6493,10 +6506,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555776</v>
+        <v>555770</v>
       </c>
       <c r="R54" t="n">
-        <v>6696866</v>
+        <v>6696857</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6555,54 +6568,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080516</v>
+        <v>129080509</v>
       </c>
       <c r="B55" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555717</v>
+        <v>555776</v>
       </c>
       <c r="R55" t="n">
-        <v>6696796</v>
+        <v>6696866</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6661,42 +6665,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080514</v>
+        <v>129080499</v>
       </c>
       <c r="B56" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555713</v>
+        <v>555799</v>
       </c>
       <c r="R56" t="n">
-        <v>6696791</v>
+        <v>6696875</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7164,45 +7164,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080506</v>
+        <v>129080518</v>
       </c>
       <c r="B61" t="n">
-        <v>92196</v>
+        <v>92871</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>483</v>
+        <v>5964</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555779</v>
+        <v>555789</v>
       </c>
       <c r="R61" t="n">
-        <v>6696887</v>
+        <v>6696889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7261,10 +7270,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080515</v>
+        <v>129080506</v>
       </c>
       <c r="B62" t="n">
-        <v>98727</v>
+        <v>92196</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7272,43 +7281,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555725</v>
+        <v>555779</v>
       </c>
       <c r="R62" t="n">
-        <v>6696807</v>
+        <v>6696887</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,42 +7367,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080518</v>
+        <v>129080515</v>
       </c>
       <c r="B63" t="n">
-        <v>92871</v>
+        <v>98727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555789</v>
+        <v>555725</v>
       </c>
       <c r="R63" t="n">
-        <v>6696889</v>
+        <v>6696807</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5663,48 +5663,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080521</v>
+        <v>129080497</v>
       </c>
       <c r="B46" t="n">
-        <v>86892</v>
+        <v>91553</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>442</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555798</v>
+        <v>555735</v>
       </c>
       <c r="R46" t="n">
-        <v>6696849</v>
+        <v>6696818</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5739,18 +5736,12 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ingen reaktion med KOH.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5769,45 +5760,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080497</v>
+        <v>129080521</v>
       </c>
       <c r="B47" t="n">
-        <v>91553</v>
+        <v>86892</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555735</v>
+        <v>555798</v>
       </c>
       <c r="R47" t="n">
-        <v>6696818</v>
+        <v>6696849</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5842,12 +5836,18 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ingen reaktion med KOH.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129080504</v>
+        <v>129080496</v>
       </c>
       <c r="B50" t="n">
-        <v>92006</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555776</v>
+        <v>555738</v>
       </c>
       <c r="R50" t="n">
-        <v>6696786</v>
+        <v>6696882</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129080496</v>
+        <v>129080504</v>
       </c>
       <c r="B51" t="n">
-        <v>91553</v>
+        <v>92006</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555738</v>
+        <v>555776</v>
       </c>
       <c r="R51" t="n">
-        <v>6696882</v>
+        <v>6696786</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6259,54 +6259,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080516</v>
+        <v>129080508</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555717</v>
+        <v>555770</v>
       </c>
       <c r="R52" t="n">
-        <v>6696796</v>
+        <v>6696857</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6365,54 +6356,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080514</v>
+        <v>129080509</v>
       </c>
       <c r="B53" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555713</v>
+        <v>555776</v>
       </c>
       <c r="R53" t="n">
-        <v>6696791</v>
+        <v>6696866</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6471,10 +6453,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080508</v>
+        <v>129080499</v>
       </c>
       <c r="B54" t="n">
-        <v>91851</v>
+        <v>57887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6482,34 +6464,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555770</v>
+        <v>555799</v>
       </c>
       <c r="R54" t="n">
-        <v>6696857</v>
+        <v>6696875</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6568,45 +6555,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080509</v>
+        <v>129080516</v>
       </c>
       <c r="B55" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555776</v>
+        <v>555717</v>
       </c>
       <c r="R55" t="n">
-        <v>6696866</v>
+        <v>6696796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6665,38 +6661,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080499</v>
+        <v>129080514</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555799</v>
+        <v>555713</v>
       </c>
       <c r="R56" t="n">
-        <v>6696875</v>
+        <v>6696791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7270,10 +7270,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080506</v>
+        <v>129080515</v>
       </c>
       <c r="B62" t="n">
-        <v>92196</v>
+        <v>98727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7281,34 +7281,43 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555779</v>
+        <v>555725</v>
       </c>
       <c r="R62" t="n">
-        <v>6696887</v>
+        <v>6696807</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,10 +7376,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080515</v>
+        <v>129080506</v>
       </c>
       <c r="B63" t="n">
-        <v>98727</v>
+        <v>92196</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7378,43 +7387,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555725</v>
+        <v>555779</v>
       </c>
       <c r="R63" t="n">
-        <v>6696807</v>
+        <v>6696887</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -6259,45 +6259,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080508</v>
+        <v>129080516</v>
       </c>
       <c r="B52" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555770</v>
+        <v>555717</v>
       </c>
       <c r="R52" t="n">
-        <v>6696857</v>
+        <v>6696796</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6356,45 +6365,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080509</v>
+        <v>129080514</v>
       </c>
       <c r="B53" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555776</v>
+        <v>555713</v>
       </c>
       <c r="R53" t="n">
-        <v>6696866</v>
+        <v>6696791</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6453,10 +6471,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080499</v>
+        <v>129080508</v>
       </c>
       <c r="B54" t="n">
-        <v>57887</v>
+        <v>91851</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6464,39 +6482,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555799</v>
+        <v>555770</v>
       </c>
       <c r="R54" t="n">
-        <v>6696875</v>
+        <v>6696857</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6555,54 +6568,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080516</v>
+        <v>129080509</v>
       </c>
       <c r="B55" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555717</v>
+        <v>555776</v>
       </c>
       <c r="R55" t="n">
-        <v>6696796</v>
+        <v>6696866</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6661,42 +6665,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080514</v>
+        <v>129080499</v>
       </c>
       <c r="B56" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555713</v>
+        <v>555799</v>
       </c>
       <c r="R56" t="n">
-        <v>6696791</v>
+        <v>6696875</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080510</v>
+        <v>129080493</v>
       </c>
       <c r="B57" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6778,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555735</v>
+        <v>555776</v>
       </c>
       <c r="R57" t="n">
-        <v>6696835</v>
+        <v>6696784</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080493</v>
+        <v>129080510</v>
       </c>
       <c r="B58" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555776</v>
+        <v>555735</v>
       </c>
       <c r="R58" t="n">
-        <v>6696784</v>
+        <v>6696835</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7164,54 +7164,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080518</v>
+        <v>129080506</v>
       </c>
       <c r="B61" t="n">
-        <v>92871</v>
+        <v>92196</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5964</v>
+        <v>483</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555789</v>
+        <v>555779</v>
       </c>
       <c r="R61" t="n">
-        <v>6696889</v>
+        <v>6696887</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7270,42 +7261,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080515</v>
+        <v>129080518</v>
       </c>
       <c r="B62" t="n">
-        <v>98727</v>
+        <v>92871</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7314,10 +7305,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555725</v>
+        <v>555789</v>
       </c>
       <c r="R62" t="n">
-        <v>6696807</v>
+        <v>6696889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7376,10 +7367,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080506</v>
+        <v>129080515</v>
       </c>
       <c r="B63" t="n">
-        <v>92196</v>
+        <v>98727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7387,34 +7378,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555779</v>
+        <v>555725</v>
       </c>
       <c r="R63" t="n">
-        <v>6696887</v>
+        <v>6696807</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5663,45 +5663,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080497</v>
+        <v>129080521</v>
       </c>
       <c r="B46" t="n">
-        <v>91553</v>
+        <v>86892</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555735</v>
+        <v>555798</v>
       </c>
       <c r="R46" t="n">
-        <v>6696818</v>
+        <v>6696849</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5736,12 +5739,18 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ingen reaktion med KOH.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5760,48 +5769,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080521</v>
+        <v>129080497</v>
       </c>
       <c r="B47" t="n">
-        <v>86892</v>
+        <v>91553</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>442</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555798</v>
+        <v>555735</v>
       </c>
       <c r="R47" t="n">
-        <v>6696849</v>
+        <v>6696818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5836,18 +5842,12 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ingen reaktion med KOH.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129080496</v>
+        <v>129080504</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>92006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555738</v>
+        <v>555776</v>
       </c>
       <c r="R50" t="n">
-        <v>6696882</v>
+        <v>6696786</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129080504</v>
+        <v>129080496</v>
       </c>
       <c r="B51" t="n">
-        <v>92006</v>
+        <v>91553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555776</v>
+        <v>555738</v>
       </c>
       <c r="R51" t="n">
-        <v>6696786</v>
+        <v>6696882</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080493</v>
+        <v>129080510</v>
       </c>
       <c r="B57" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6778,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555776</v>
+        <v>555735</v>
       </c>
       <c r="R57" t="n">
-        <v>6696784</v>
+        <v>6696835</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080510</v>
+        <v>129080493</v>
       </c>
       <c r="B58" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6875,21 +6875,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555735</v>
+        <v>555776</v>
       </c>
       <c r="R58" t="n">
-        <v>6696835</v>
+        <v>6696784</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -5075,7 +5075,7 @@
         <v>129080492</v>
       </c>
       <c r="B40" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129080512</v>
       </c>
       <c r="B41" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>129080494</v>
       </c>
       <c r="B42" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>129080505</v>
       </c>
       <c r="B43" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129080491</v>
       </c>
       <c r="B44" t="n">
-        <v>91777</v>
+        <v>91805</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>129080517</v>
       </c>
       <c r="B45" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5663,48 +5663,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080521</v>
+        <v>129080497</v>
       </c>
       <c r="B46" t="n">
-        <v>86892</v>
+        <v>91581</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>442</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555798</v>
+        <v>555735</v>
       </c>
       <c r="R46" t="n">
-        <v>6696849</v>
+        <v>6696818</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5739,18 +5736,12 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ingen reaktion med KOH.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5769,45 +5760,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080497</v>
+        <v>129080521</v>
       </c>
       <c r="B47" t="n">
-        <v>91553</v>
+        <v>86920</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555735</v>
+        <v>555798</v>
       </c>
       <c r="R47" t="n">
-        <v>6696818</v>
+        <v>6696849</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5842,12 +5836,18 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ingen reaktion med KOH.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>129080511</v>
       </c>
       <c r="B48" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>129080498</v>
       </c>
       <c r="B49" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>129080504</v>
       </c>
       <c r="B50" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>129080496</v>
       </c>
       <c r="B51" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6259,54 +6259,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080516</v>
+        <v>129080508</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>91879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555717</v>
+        <v>555770</v>
       </c>
       <c r="R52" t="n">
-        <v>6696796</v>
+        <v>6696857</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6365,54 +6356,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080514</v>
+        <v>129080509</v>
       </c>
       <c r="B53" t="n">
-        <v>98727</v>
+        <v>91879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555713</v>
+        <v>555776</v>
       </c>
       <c r="R53" t="n">
-        <v>6696791</v>
+        <v>6696866</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6471,10 +6453,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080508</v>
+        <v>129080499</v>
       </c>
       <c r="B54" t="n">
-        <v>91851</v>
+        <v>57890</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6482,34 +6464,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555770</v>
+        <v>555799</v>
       </c>
       <c r="R54" t="n">
-        <v>6696857</v>
+        <v>6696875</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6568,45 +6555,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080509</v>
+        <v>129080516</v>
       </c>
       <c r="B55" t="n">
-        <v>91851</v>
+        <v>98756</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555776</v>
+        <v>555717</v>
       </c>
       <c r="R55" t="n">
-        <v>6696866</v>
+        <v>6696796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6665,38 +6661,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080499</v>
+        <v>129080514</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>98756</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555799</v>
+        <v>555713</v>
       </c>
       <c r="R56" t="n">
-        <v>6696875</v>
+        <v>6696791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6770,7 +6770,7 @@
         <v>129080510</v>
       </c>
       <c r="B57" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>129080493</v>
       </c>
       <c r="B58" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>129080522</v>
       </c>
       <c r="B59" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>129080503</v>
       </c>
       <c r="B60" t="n">
-        <v>92847</v>
+        <v>92875</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7164,45 +7164,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080506</v>
+        <v>129080518</v>
       </c>
       <c r="B61" t="n">
-        <v>92196</v>
+        <v>92899</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>483</v>
+        <v>5964</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555779</v>
+        <v>555789</v>
       </c>
       <c r="R61" t="n">
-        <v>6696887</v>
+        <v>6696889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7261,54 +7270,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080518</v>
+        <v>129080506</v>
       </c>
       <c r="B62" t="n">
-        <v>92871</v>
+        <v>92224</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5964</v>
+        <v>483</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555789</v>
+        <v>555779</v>
       </c>
       <c r="R62" t="n">
-        <v>6696889</v>
+        <v>6696887</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7370,7 +7370,7 @@
         <v>129080515</v>
       </c>
       <c r="B63" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555781.6479232884</v>
+        <v>555782</v>
       </c>
       <c r="R2" t="n">
-        <v>6696842.323452283</v>
+        <v>6696842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2018-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93030</v>
+        <v>93032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93032</v>
+        <v>93036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93036</v>
+        <v>93049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93049</v>
+        <v>93050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93050</v>
+        <v>93051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93051</v>
+        <v>93060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>75467725</v>
       </c>
       <c r="B2" t="n">
-        <v>93084</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97329446</v>
+        <v>129080521</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,52 +787,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555780.0583261261</v>
+        <v>555798</v>
       </c>
       <c r="R3" t="n">
-        <v>6696881.340733854</v>
+        <v>6696849</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +844,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ingen reaktion med KOH.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,72 +863,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97328790</v>
+        <v>129080506</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>483</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555769.7703942264</v>
+        <v>555779</v>
       </c>
       <c r="R4" t="n">
-        <v>6696842.140949611</v>
+        <v>6696887</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,56 +979,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97329495</v>
+        <v>97329307</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555738.3683355377</v>
+        <v>555780</v>
       </c>
       <c r="R5" t="n">
-        <v>6696791.743951798</v>
+        <v>6696881</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,7 +1060,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1070,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,33 +1079,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97329335</v>
+        <v>124288655</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,38 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555780.0583261261</v>
+        <v>555733</v>
       </c>
       <c r="R6" t="n">
-        <v>6696881.340733854</v>
+        <v>6696827</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,22 +1163,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,66 +1183,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97328867</v>
+        <v>124288656</v>
       </c>
       <c r="B7" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555753.1368644732</v>
+        <v>555769</v>
       </c>
       <c r="R7" t="n">
-        <v>6696893.776213734</v>
+        <v>6696795</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,22 +1260,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:39</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:39</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,15 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97329167</v>
+        <v>129080508</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,38 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555826.8146765307</v>
+        <v>555770</v>
       </c>
       <c r="R8" t="n">
-        <v>6696898.862166425</v>
+        <v>6696857</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,22 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97328938</v>
+        <v>129080509</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,38 +1400,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555780.4910950072</v>
+        <v>555776</v>
       </c>
       <c r="R9" t="n">
-        <v>6696853.178092062</v>
+        <v>6696866</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,22 +1454,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,15 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97328750</v>
+        <v>129080510</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,38 +1497,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555725.2940785955</v>
+        <v>555735</v>
       </c>
       <c r="R10" t="n">
-        <v>6696901.749964267</v>
+        <v>6696835</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,22 +1551,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,15 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97328832</v>
+        <v>129080511</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,38 +1594,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555779.2203884723</v>
+        <v>555738</v>
       </c>
       <c r="R11" t="n">
-        <v>6696871.44392027</v>
+        <v>6696821</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1770,22 +1648,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,64 +1680,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97329511</v>
+        <v>129080512</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tomsbovägen, Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555733.5558447185</v>
+        <v>555776</v>
       </c>
       <c r="R12" t="n">
-        <v>6696782.774302922</v>
+        <v>6696786</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1893,22 +1745,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,66 +1765,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97329169</v>
+        <v>129080491</v>
       </c>
       <c r="B13" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555826.8146765307</v>
+        <v>555770</v>
       </c>
       <c r="R13" t="n">
-        <v>6696898.862166425</v>
+        <v>6696850</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2006,22 +1842,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,49 +1874,35 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97328720</v>
+        <v>97328558</v>
       </c>
       <c r="B14" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2098,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555718.9818685917</v>
+        <v>555736</v>
       </c>
       <c r="R14" t="n">
-        <v>6696893.745966963</v>
+        <v>6696813</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,7 +1945,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +1955,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,62 +1982,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97328646</v>
+        <v>97328741</v>
       </c>
       <c r="B15" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555765.5379620116</v>
+        <v>555721</v>
       </c>
       <c r="R15" t="n">
-        <v>6696859.867134871</v>
+        <v>6696895</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2257,7 +2053,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2063,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,34 +2072,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97328741</v>
+        <v>97328747</v>
       </c>
       <c r="B16" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555720.9462597554</v>
+        <v>555725</v>
       </c>
       <c r="R16" t="n">
-        <v>6696894.764509278</v>
+        <v>6696902</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2371,7 +2161,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2171,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,52 +2198,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97329508</v>
+        <v>97328938</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tomsbovägen, Hedemora, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555711.9280991431</v>
+        <v>555781</v>
       </c>
       <c r="R17" t="n">
-        <v>6696837.299124204</v>
+        <v>6696853</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2485,7 +2269,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2495,7 +2279,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2522,52 +2306,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97329475</v>
+        <v>97329167</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tomsbovägen, Hedemora, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555730.4347018026</v>
+        <v>555827</v>
       </c>
       <c r="R18" t="n">
-        <v>6696792.610557184</v>
+        <v>6696899</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2599,7 +2377,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,7 +2387,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,15 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97328558</v>
+        <v>97329314</v>
       </c>
       <c r="B19" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555736.0473321147</v>
+        <v>555818</v>
       </c>
       <c r="R19" t="n">
-        <v>6696813.947612317</v>
+        <v>6696879</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2712,7 +2485,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2722,7 +2495,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,15 +2522,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97329314</v>
+        <v>97329335</v>
       </c>
       <c r="B20" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555818.1953765308</v>
+        <v>555780</v>
       </c>
       <c r="R20" t="n">
-        <v>6696879.950192579</v>
+        <v>6696881</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2825,7 +2593,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2603,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,68 +2618,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97328989</v>
+        <v>124288644</v>
       </c>
       <c r="B21" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555813.2464571904</v>
+        <v>555774</v>
       </c>
       <c r="R21" t="n">
-        <v>6696879.87409499</v>
+        <v>6696769</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2935,22 +2695,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,7 +2709,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2978,55 +2727,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97328610</v>
+        <v>124288645</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555727.6889716892</v>
+        <v>555769</v>
       </c>
       <c r="R22" t="n">
-        <v>6696842.483068235</v>
+        <v>6696795</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3050,22 +2792,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3092,64 +2824,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97401155</v>
+        <v>124288646</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555773.8814013347</v>
+        <v>555732</v>
       </c>
       <c r="R23" t="n">
-        <v>6696832.320069506</v>
+        <v>6696815</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3173,22 +2889,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3203,80 +2909,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97401158</v>
+        <v>129080493</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555814.0235234372</v>
+        <v>555776</v>
       </c>
       <c r="R24" t="n">
-        <v>6696893.723520528</v>
+        <v>6696784</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3300,22 +2986,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,68 +3006,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97328738</v>
+        <v>129080494</v>
       </c>
       <c r="B25" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5685</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555765.5379620116</v>
+        <v>555786</v>
       </c>
       <c r="R25" t="n">
-        <v>6696859.867134871</v>
+        <v>6696881</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3415,107 +3083,80 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97401177</v>
+        <v>129080496</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555755.2573976177</v>
+        <v>555738</v>
       </c>
       <c r="R26" t="n">
-        <v>6696820.17307734</v>
+        <v>6696882</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3539,22 +3180,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3569,75 +3200,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97401037</v>
+        <v>129080497</v>
       </c>
       <c r="B27" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555790.6029287559</v>
+        <v>555735</v>
       </c>
       <c r="R27" t="n">
-        <v>6696871.618847977</v>
+        <v>6696818</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3661,22 +3277,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3691,75 +3297,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97413040</v>
+        <v>124288654</v>
       </c>
       <c r="B28" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555813.1552940429</v>
+        <v>555776</v>
       </c>
       <c r="R28" t="n">
-        <v>6696885.803047111</v>
+        <v>6696789</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3783,22 +3374,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3813,80 +3394,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97413149</v>
+        <v>129080504</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tomsbovägen, Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555719.9374721729</v>
+        <v>555776</v>
       </c>
       <c r="R29" t="n">
-        <v>6696831.49163196</v>
+        <v>6696786</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3910,22 +3471,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3940,72 +3491,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>97412989</v>
+        <v>129080505</v>
       </c>
       <c r="B30" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555816.6336634106</v>
+        <v>555779</v>
       </c>
       <c r="R30" t="n">
-        <v>6696852.745265569</v>
+        <v>6696888</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4029,29 +3568,19 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -4059,77 +3588,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>97412931</v>
+        <v>97328989</v>
       </c>
       <c r="B31" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555817.5778696365</v>
+        <v>555814</v>
       </c>
       <c r="R31" t="n">
-        <v>6696855.724984788</v>
+        <v>6696880</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4156,22 +3668,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4180,55 +3692,51 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>97412958</v>
+        <v>97401037</v>
       </c>
       <c r="B32" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4236,23 +3744,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555808.6697553289</v>
+        <v>555790</v>
       </c>
       <c r="R32" t="n">
-        <v>6696855.5880158</v>
+        <v>6696872</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4279,22 +3786,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
+          <t>2021-12-04</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
+          <t>2021-12-04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4309,49 +3816,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>97329307</v>
+        <v>97413040</v>
       </c>
       <c r="B33" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4361,21 +3863,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555780.0583261261</v>
+        <v>555813</v>
       </c>
       <c r="R33" t="n">
-        <v>6696881.340733854</v>
+        <v>6696885</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4402,22 +3903,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
+          <t>2021-12-05</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2021-11-28</t>
+          <t>2021-12-05</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4426,7 +3927,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4445,15 +3945,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124288656</v>
+        <v>129080502</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4461,21 +3956,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4485,10 +3980,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555769</v>
+        <v>555799</v>
       </c>
       <c r="R34" t="n">
-        <v>6696795</v>
+        <v>6696929</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4515,12 +4010,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4547,15 +4042,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124288655</v>
+        <v>129080503</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4563,21 +4053,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4077,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555733</v>
+        <v>555761</v>
       </c>
       <c r="R35" t="n">
-        <v>6696827</v>
+        <v>6696908</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4617,12 +4107,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4649,53 +4139,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124288646</v>
+        <v>97329169</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555732</v>
+        <v>555827</v>
       </c>
       <c r="R36" t="n">
-        <v>6696815</v>
+        <v>6696899</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4719,12 +4205,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4751,37 +4247,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124288644</v>
+        <v>129080492</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4791,10 +4282,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555774</v>
+        <v>555785</v>
       </c>
       <c r="R37" t="n">
-        <v>6696769</v>
+        <v>6696895</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4821,12 +4312,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4853,53 +4344,51 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124288654</v>
+        <v>97328738</v>
       </c>
       <c r="B38" t="n">
-        <v>91457</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>5685</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555776</v>
+        <v>555766</v>
       </c>
       <c r="R38" t="n">
-        <v>6696789</v>
+        <v>6696860</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4923,47 +4412,53 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124288645</v>
+        <v>97328720</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4971,37 +4466,47 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555769</v>
+        <v>555719</v>
       </c>
       <c r="R39" t="n">
-        <v>6696795</v>
+        <v>6696894</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5025,12 +4530,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5057,48 +4572,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129080492</v>
+        <v>97328867</v>
       </c>
       <c r="B40" t="n">
-        <v>91545</v>
+        <v>93233</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555785</v>
+        <v>555753</v>
       </c>
       <c r="R40" t="n">
-        <v>6696895</v>
+        <v>6696894</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5122,12 +4638,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5154,10 +4680,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129080512</v>
+        <v>97329113</v>
       </c>
       <c r="B41" t="n">
-        <v>91879</v>
+        <v>93233</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5165,37 +4691,47 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555776</v>
+        <v>555787</v>
       </c>
       <c r="R41" t="n">
-        <v>6696786</v>
+        <v>6696933</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5219,12 +4755,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5251,10 +4797,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129080494</v>
+        <v>129080517</v>
       </c>
       <c r="B42" t="n">
-        <v>91581</v>
+        <v>93233</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5262,34 +4808,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555786</v>
+        <v>555773</v>
       </c>
       <c r="R42" t="n">
-        <v>6696881</v>
+        <v>6696900</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5348,45 +4903,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129080505</v>
+        <v>129080518</v>
       </c>
       <c r="B43" t="n">
-        <v>92034</v>
+        <v>93233</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555779</v>
+        <v>555789</v>
       </c>
       <c r="R43" t="n">
-        <v>6696888</v>
+        <v>6696889</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5445,45 +5009,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129080491</v>
+        <v>129080519</v>
       </c>
       <c r="B44" t="n">
-        <v>91805</v>
+        <v>93233</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1106</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555770</v>
+        <v>555840</v>
       </c>
       <c r="R44" t="n">
-        <v>6696850</v>
+        <v>6696854</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5542,57 +5115,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129080517</v>
+        <v>97329490</v>
       </c>
       <c r="B45" t="n">
-        <v>92899</v>
+        <v>93235</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Tomsbovägen, Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555773</v>
+        <v>555697</v>
       </c>
       <c r="R45" t="n">
-        <v>6696900</v>
+        <v>6696808</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5616,12 +5181,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5648,48 +5223,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129080497</v>
+        <v>97328790</v>
       </c>
       <c r="B46" t="n">
-        <v>91581</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555735</v>
+        <v>555770</v>
       </c>
       <c r="R46" t="n">
-        <v>6696818</v>
+        <v>6696842</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5713,12 +5289,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5745,10 +5331,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129080521</v>
+        <v>97328832</v>
       </c>
       <c r="B47" t="n">
-        <v>86920</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5756,40 +5342,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>442</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555798</v>
+        <v>555779</v>
       </c>
       <c r="R47" t="n">
-        <v>6696849</v>
+        <v>6696871</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5813,17 +5397,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ingen reaktion med KOH.</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5832,7 +5421,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5851,48 +5439,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129080511</v>
+        <v>97329051</v>
       </c>
       <c r="B48" t="n">
-        <v>91879</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555738</v>
+        <v>555791</v>
       </c>
       <c r="R48" t="n">
-        <v>6696821</v>
+        <v>6696931</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5916,12 +5505,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5948,53 +5547,59 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129080498</v>
+        <v>97412958</v>
       </c>
       <c r="B49" t="n">
-        <v>57890</v>
+        <v>57950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555757</v>
+        <v>555808</v>
       </c>
       <c r="R49" t="n">
-        <v>6696784</v>
+        <v>6696856</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6018,12 +5623,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6038,60 +5653,67 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129080504</v>
+        <v>97412989</v>
       </c>
       <c r="B50" t="n">
-        <v>92034</v>
+        <v>5179</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555776</v>
+        <v>555816</v>
       </c>
       <c r="R50" t="n">
-        <v>6696786</v>
+        <v>6696852</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6115,19 +5737,29 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
@@ -6135,22 +5767,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129080496</v>
+        <v>129080498</v>
       </c>
       <c r="B51" t="n">
-        <v>91581</v>
+        <v>58114</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6158,34 +5790,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555738</v>
+        <v>555757</v>
       </c>
       <c r="R51" t="n">
-        <v>6696882</v>
+        <v>6696784</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6244,10 +5881,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129080508</v>
+        <v>129080499</v>
       </c>
       <c r="B52" t="n">
-        <v>91879</v>
+        <v>58114</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6255,34 +5892,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555770</v>
+        <v>555799</v>
       </c>
       <c r="R52" t="n">
-        <v>6696857</v>
+        <v>6696875</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6341,48 +5983,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129080509</v>
+        <v>97328610</v>
       </c>
       <c r="B53" t="n">
-        <v>91879</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555776</v>
+        <v>555728</v>
       </c>
       <c r="R53" t="n">
-        <v>6696866</v>
+        <v>6696843</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6406,12 +6050,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6438,53 +6092,63 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129080499</v>
+        <v>97329094</v>
       </c>
       <c r="B54" t="n">
-        <v>57890</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555799</v>
+        <v>555780</v>
       </c>
       <c r="R54" t="n">
-        <v>6696875</v>
+        <v>6696881</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6508,12 +6172,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6528,22 +6202,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129080516</v>
+        <v>97329266</v>
       </c>
       <c r="B55" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6570,7 +6244,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6578,19 +6252,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555717</v>
+        <v>555847</v>
       </c>
       <c r="R55" t="n">
-        <v>6696796</v>
+        <v>6696871</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6614,12 +6290,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6634,22 +6320,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129080514</v>
+        <v>97329475</v>
       </c>
       <c r="B56" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6674,29 +6360,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Tomsbovägen, Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555713</v>
+        <v>555730</v>
       </c>
       <c r="R56" t="n">
-        <v>6696791</v>
+        <v>6696793</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6720,12 +6399,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6752,48 +6441,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129080510</v>
+        <v>97329495</v>
       </c>
       <c r="B57" t="n">
-        <v>91879</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555735</v>
+        <v>555738</v>
       </c>
       <c r="R57" t="n">
-        <v>6696835</v>
+        <v>6696792</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6817,12 +6512,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6837,60 +6542,62 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129080493</v>
+        <v>97329508</v>
       </c>
       <c r="B58" t="n">
-        <v>91581</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Tomsbovägen, Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555776</v>
+        <v>555712</v>
       </c>
       <c r="R58" t="n">
-        <v>6696784</v>
+        <v>6696837</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6914,12 +6621,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6946,10 +6663,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129080522</v>
+        <v>97329511</v>
       </c>
       <c r="B59" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6976,7 +6693,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6984,19 +6701,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Tomsbovägen, Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555744</v>
+        <v>555733</v>
       </c>
       <c r="R59" t="n">
-        <v>6696814</v>
+        <v>6696783</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7020,12 +6739,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7040,60 +6769,71 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129080503</v>
+        <v>97401155</v>
       </c>
       <c r="B60" t="n">
-        <v>92875</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555761</v>
+        <v>555774</v>
       </c>
       <c r="R60" t="n">
-        <v>6696908</v>
+        <v>6696832</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7117,12 +6857,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7137,69 +6887,75 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129080518</v>
+        <v>97401158</v>
       </c>
       <c r="B61" t="n">
-        <v>92899</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555789</v>
+        <v>555814</v>
       </c>
       <c r="R61" t="n">
-        <v>6696889</v>
+        <v>6696894</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7223,12 +6979,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7243,22 +7009,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129080506</v>
+        <v>97401177</v>
       </c>
       <c r="B62" t="n">
-        <v>92224</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7266,37 +7032,48 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555779</v>
+        <v>555755</v>
       </c>
       <c r="R62" t="n">
-        <v>6696887</v>
+        <v>6696820</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7320,12 +7097,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7340,22 +7127,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129080515</v>
+        <v>97412931</v>
       </c>
       <c r="B63" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7382,7 +7169,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7390,19 +7177,25 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555725</v>
+        <v>555818</v>
       </c>
       <c r="R63" t="n">
-        <v>6696807</v>
+        <v>6696855</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7426,12 +7219,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7446,15 +7249,681 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>97413149</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Tomsbovägen, Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>555719</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6696831</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2021-12-05</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129080514</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>555713</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6696791</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129080515</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>555725</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6696807</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129080516</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>555717</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6696796</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129080522</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>555744</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6696814</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>97328646</v>
+      </c>
+      <c r="B69" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>555766</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6696860</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42345-2023 artfynd.xlsx
+++ b/artfynd/A 42345-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75467725</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080521</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080506</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329307</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124288655</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124288656</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080508</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080509</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080510</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080511</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080512</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080491</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1979,6 +2044,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328558</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2087,6 +2157,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328741</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2195,6 +2270,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328747</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2303,6 +2383,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328938</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2411,6 +2496,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329167</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2519,6 +2609,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329314</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2627,6 +2722,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329335</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2724,6 +2824,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124288644</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2821,6 +2926,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124288645</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2918,6 +3028,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124288646</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3015,6 +3130,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080493</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3112,6 +3232,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080494</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3209,6 +3334,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080496</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3306,6 +3436,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080497</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3403,6 +3538,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124288654</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3500,6 +3640,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080504</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3597,6 +3742,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080505</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3708,6 +3858,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328989</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3825,6 +3980,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97401037</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3942,6 +4102,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97413040</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4039,6 +4204,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080502</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4136,6 +4306,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080503</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4244,6 +4419,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329169</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4341,6 +4521,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080492</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4452,6 +4637,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328738</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4569,6 +4759,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328720</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4677,6 +4872,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328867</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4794,6 +4994,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329113</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4900,6 +5105,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080517</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5006,6 +5216,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080518</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5112,6 +5327,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080519</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5220,6 +5440,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329490</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5328,6 +5553,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328790</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5436,6 +5666,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328832</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5544,6 +5779,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329051</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5662,6 +5902,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97412958</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5776,6 +6021,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97412989</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5878,6 +6128,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080498</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5980,6 +6235,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080499</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6089,6 +6349,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328610</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6211,6 +6476,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329094</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6329,6 +6599,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329266</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6438,6 +6713,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329475</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6551,6 +6831,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329495</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6660,6 +6945,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329508</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6778,6 +7068,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97329511</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6896,6 +7191,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97401155</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7018,6 +7318,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97401158</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7136,6 +7441,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97401177</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7258,6 +7568,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97412931</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7380,6 +7695,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97413149</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7486,6 +7806,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080514</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7592,6 +7917,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080515</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7698,6 +8028,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080516</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7804,6 +8139,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129080522</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7924,8 +8264,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97328646</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>